--- a/registration_forms/032_yoga_registration_and_waiver_form--registration_forms.xlsx
+++ b/registration_forms/032_yoga_registration_and_waiver_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>emergency_contact_relationship_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Emergency Contact Relationship 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Emergency Contact Phone Relationship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Emergency Contact Name Relationship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>emergency_authorization</t>
+          <t>emergency_authorization_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emergency Authorization</t>
+          <t>Emergency Authorization 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>emergency_medical_insurance</t>
+          <t>emergency_medical_insurance_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emergency Medical Insurance</t>
+          <t>Emergency Medical Insurance 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,1285 +1369,418 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_dob_year_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_dob_year_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_dob_year_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>son</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Son</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>daughter</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Daughter</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_phone_relationship_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_phone_relationship_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_phone_relationship_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_phone_relationship_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>son</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Son</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_phone_relationship_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>daughter</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Daughter</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_phone_relationship_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_phone_relationship_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_name_relationship_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_name_relationship_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_name_relationship_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_name_relationship_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>son</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Son</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_name_relationship_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>daughter</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Daughter</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_name_relationship_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>emergency_contact_dob_day_choices</t>
+          <t>emergency_contact_name_relationship_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_day_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_day_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_day_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_day_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>emergency_contact_dob_year_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>mother</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>father</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>spouse</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Spouse</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>son</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Son</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>daughter</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Daughter</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>father</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>mother</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>spouse</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Spouse</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>son</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Son</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>daughter</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Daughter</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>emergency_contact_name_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>father</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>emergency_contact_name_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>mother</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>emergency_contact_name_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>spouse</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Spouse</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>emergency_contact_name_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>son</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Son</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>emergency_contact_name_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>daughter</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Daughter</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>emergency_contact_name_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>emergency_contact_name_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
         <is>
           <t>None</t>
         </is>
